--- a/astro-site/public/dl/guia-panaderia-obrador/pl-mensual-escenarios.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/pl-mensual-escenarios.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L 3 escenarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'P&amp;L 3 escenarios'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -448,7 +450,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -467,6 +469,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -551,7 +554,6 @@
       <c r="D6" t="n">
         <v>28</v>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -561,17 +563,16 @@
       </c>
       <c r="B7">
         <f>B4*B5*B6</f>
-        <v/>
+        <v>16224.0</v>
       </c>
       <c r="C7">
         <f>C4*C5*C6</f>
-        <v/>
+        <v>32480.0</v>
       </c>
       <c r="D7">
         <f>D4*D5*D6</f>
-        <v/>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>56448.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,25 +603,18 @@
       </c>
       <c r="B9">
         <f>B7+B8</f>
-        <v/>
+        <v>17724.0</v>
       </c>
       <c r="C9">
         <f>C7+C8</f>
-        <v/>
+        <v>37280.0</v>
       </c>
       <c r="D9">
         <f>D7+D8</f>
-        <v/>
-      </c>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-    </row>
+        <v>66248.0</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -636,7 +630,6 @@
       <c r="D11" t="n">
         <v>0.18</v>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -646,17 +639,16 @@
       </c>
       <c r="B12">
         <f>B9*B11</f>
-        <v/>
+        <v>3899.28</v>
       </c>
       <c r="C12">
         <f>C9*C11</f>
-        <v/>
+        <v>7456.0</v>
       </c>
       <c r="D12">
         <f>D9*D11</f>
-        <v/>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>11924.64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -736,7 +728,6 @@
       <c r="D16" t="n">
         <v>1200</v>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -746,17 +737,16 @@
       </c>
       <c r="B17">
         <f>SUM(B12:B16)</f>
-        <v/>
+        <v>17499.28</v>
       </c>
       <c r="C17">
         <f>SUM(C12:C16)</f>
-        <v/>
+        <v>23856.0</v>
       </c>
       <c r="D17">
         <f>SUM(D12:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>30424.64</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -766,17 +756,16 @@
       </c>
       <c r="B18">
         <f>B9-B17</f>
-        <v/>
+        <v>224.72000000000116</v>
       </c>
       <c r="C18">
         <f>C9-C17</f>
-        <v/>
+        <v>13424.0</v>
       </c>
       <c r="D18">
         <f>D9-D17</f>
-        <v/>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>35823.36</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -786,22 +775,30 @@
       </c>
       <c r="B19">
         <f>B18*12</f>
-        <v/>
+        <v>2696.640000000014</v>
       </c>
       <c r="C19">
         <f>C18*12</f>
-        <v/>
+        <v>161088.0</v>
       </c>
       <c r="D19">
         <f>D18*12</f>
-        <v/>
-      </c>
-      <c r="E19" t="inlineStr"/>
+        <v>429880.32</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>